--- a/MAJSushiConfig/ig/StructureDefinition-fr-bundle-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-bundle-document.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-bundle-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-bundle-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -888,7 +888,7 @@
     <t>Bundle.entry:composition.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Composition {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-composition-document|0.1.0}
+    <t xml:space="preserve">Composition {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-composition-document|0.1.0}
 </t>
   </si>
   <si>
@@ -1010,7 +1010,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Patient {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-document|0.1.0}
+    <t xml:space="preserve">Patient {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-document|0.1.0}
 </t>
   </si>
   <si>
@@ -1125,7 +1125,7 @@
     <t>Bundle.entry:practitionerRole.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">PractitionerRole {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitionerRole-document|0.1.0}
+    <t xml:space="preserve">PractitionerRole {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0}
 </t>
   </si>
   <si>
@@ -1240,7 +1240,7 @@
     <t>Bundle.entry:practitioner.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Practitioner {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitioner-document|0.1.0}
+    <t xml:space="preserve">Practitioner {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitioner-document|0.1.0}
 </t>
   </si>
   <si>
@@ -1349,7 +1349,7 @@
     <t>Bundle.entry:organization.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Organization {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-organization-document|0.1.0}
+    <t xml:space="preserve">Organization {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-organization-document|0.1.0}
 </t>
   </si>
   <si>
@@ -1464,7 +1464,7 @@
     <t>Bundle.entry:device.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Device {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-device-auteur-document|0.1.0}
+    <t xml:space="preserve">Device {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-device-auteur-document|0.1.0}
 </t>
   </si>
   <si>
@@ -1580,7 +1580,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Encounter {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-encounter-care-document|0.1.0}
+    <t xml:space="preserve">Encounter {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-encounter-care-document|0.1.0}
 </t>
   </si>
   <si>
@@ -1692,7 +1692,7 @@
     <t>Bundle.entry:location.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Location {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-location-document|0.1.0}
+    <t xml:space="preserve">Location {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-location-document|0.1.0}
 </t>
   </si>
   <si>
@@ -1804,7 +1804,7 @@
     <t>Bundle.entry:relatedPerson.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">RelatedPerson {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-related-person-document|0.1.0}
+    <t xml:space="preserve">RelatedPerson {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-related-person-document|0.1.0}
 </t>
   </si>
   <si>
@@ -2238,7 +2238,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="173.0078125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="166.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
